--- a/prototype/sample-quote.xlsx
+++ b/prototype/sample-quote.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="89">
   <si>
     <t>星辉模具制造有限公司</t>
   </si>
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-6891</t>
+    <t>报价编号：BJ-20260910-3874</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -68,33 +68,33 @@
     <t>电子邮箱</t>
   </si>
   <si>
+    <t>单件重量</t>
+  </si>
+  <si>
+    <t>0.18 kg</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>模芯长</t>
+  </si>
+  <si>
+    <t>500 mm</t>
+  </si>
+  <si>
     <t>模芯宽</t>
   </si>
   <si>
     <t>400 mm</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>模芯长</t>
-  </si>
-  <si>
-    <t>500 mm</t>
-  </si>
-  <si>
     <t>模芯高</t>
   </si>
   <si>
     <t>150 mm</t>
   </si>
   <si>
-    <t>单件重量</t>
-  </si>
-  <si>
-    <t>0.18 kg</t>
-  </si>
-  <si>
     <t>钢材单价</t>
   </si>
   <si>
@@ -107,6 +107,18 @@
     <t>7.85 g/cm³</t>
   </si>
   <si>
+    <t>原料单价</t>
+  </si>
+  <si>
+    <t>12 元/kg</t>
+  </si>
+  <si>
+    <t>注塑数量</t>
+  </si>
+  <si>
+    <t>5000 件</t>
+  </si>
+  <si>
     <t>首单数量</t>
   </si>
   <si>
@@ -125,105 +137,138 @@
     <t>计算说明</t>
   </si>
   <si>
+    <t>单价 / 单件成本</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
     <t>金额（元）</t>
   </si>
   <si>
-    <t>备注</t>
+    <t>（一）模具费用　（一次性）</t>
+  </si>
+  <si>
+    <t>模芯钢材费</t>
+  </si>
+  <si>
+    <t>模芯长 × 模芯宽 × 模芯高 → 换算重量 × 钢材单价</t>
+  </si>
+  <si>
+    <t>CNC 加工费</t>
+  </si>
+  <si>
+    <t>96 小时 × 400 元/小时</t>
+  </si>
+  <si>
+    <t>设计费</t>
+  </si>
+  <si>
+    <t>固定金额 ¥6,000</t>
+  </si>
+  <si>
+    <t>试模费</t>
+  </si>
+  <si>
+    <t>腔数 × 2500 元</t>
+  </si>
+  <si>
+    <t>管理费</t>
+  </si>
+  <si>
+    <t>模具小计 × 15%</t>
+  </si>
+  <si>
+    <t>差旅费</t>
+  </si>
+  <si>
+    <t>固定金额 ¥3,500</t>
+  </si>
+  <si>
+    <t>（二）注塑费用　（按件计价）　·　单件成本 ¥2.62 / 件　×　5,000 件</t>
+  </si>
+  <si>
+    <t>产品材料费</t>
+  </si>
+  <si>
+    <t>单件重量 × 原料单价 × (1 + 损耗 0.05)　×　注塑数量</t>
+  </si>
+  <si>
+    <t>注塑加工费</t>
+  </si>
+  <si>
+    <t>单件 ¥0.3　×　注塑数量</t>
+  </si>
+  <si>
+    <t>包装费</t>
+  </si>
+  <si>
+    <t>单件 ¥0.05　×　注塑数量</t>
+  </si>
+  <si>
+    <t>三、费用汇总</t>
+  </si>
+  <si>
+    <t>模具费用合计</t>
+  </si>
+  <si>
+    <t>注塑费用合计（单件 ¥2.62 × 5,000 件）</t>
+  </si>
+  <si>
+    <t>利润（10%）</t>
+  </si>
+  <si>
+    <t>税额（13%）</t>
+  </si>
+  <si>
+    <t>含 税 总 价</t>
+  </si>
+  <si>
+    <t>大写金额：壹拾万零叁佰零伍元伍角</t>
+  </si>
+  <si>
+    <t>四、商务条款</t>
+  </si>
+  <si>
+    <t>1. 以上总价含 13% 增值税，开具增值税专用发票。</t>
+  </si>
+  <si>
+    <t>2. 广东省内运费免费，省外按实际运输方式另行计费。</t>
+  </si>
+  <si>
+    <t>3. 模具 40 天交货，首单注塑于收到定金后 45 天交付。</t>
+  </si>
+  <si>
+    <t>本报价单经双方确认后生效。如需调整规格或数量，价格需重新核算。</t>
+  </si>
+  <si>
+    <t>供方签字（盖章）：张报价　____________________</t>
+  </si>
+  <si>
+    <t>需方签字（盖章）：____________________</t>
+  </si>
+  <si>
+    <t>计算明细 · BJ-20260910-3874</t>
+  </si>
+  <si>
+    <t>顺德电器有限公司　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件</t>
+  </si>
+  <si>
+    <t>计算方式与代入过程</t>
   </si>
   <si>
     <t>（一）模具费用</t>
   </si>
   <si>
-    <t>模芯钢材费</t>
-  </si>
-  <si>
-    <t>模芯长 × 模芯宽 × 模芯高 → 换算重量 × 钢材单价</t>
-  </si>
-  <si>
-    <t>CNC 加工费</t>
-  </si>
-  <si>
-    <t>96 小时 × 400 元/小时</t>
-  </si>
-  <si>
-    <t>设计费</t>
-  </si>
-  <si>
-    <t>固定金额 ¥6,000</t>
-  </si>
-  <si>
-    <t>试模费</t>
-  </si>
-  <si>
-    <t>腔数 × 2500 元</t>
-  </si>
-  <si>
-    <t>管理费</t>
-  </si>
-  <si>
-    <t>模具小计 × 15%</t>
-  </si>
-  <si>
-    <t>差旅费</t>
-  </si>
-  <si>
-    <t>固定金额 ¥3,500</t>
-  </si>
-  <si>
-    <t>三、费用汇总</t>
-  </si>
-  <si>
-    <t>模具费用合计</t>
-  </si>
-  <si>
-    <t>利润（10%）</t>
-  </si>
-  <si>
-    <t>税额（13%）</t>
-  </si>
-  <si>
-    <t>含 税 总 价</t>
-  </si>
-  <si>
-    <t>（人民币）</t>
-  </si>
-  <si>
-    <t>大写金额：捌万肆仟零叁拾肆元伍角</t>
-  </si>
-  <si>
-    <t>四、商务条款</t>
-  </si>
-  <si>
-    <t>1. 以上总价含 13% 增值税，开具增值税专用发票。</t>
-  </si>
-  <si>
-    <t>2. 广东省内运费免费，省外按实际运输方式另行计费。</t>
-  </si>
-  <si>
-    <t>3. 模具 40 天交货，首单注塑于收到定金后 45 天交付。</t>
-  </si>
-  <si>
-    <t>本报价单经双方确认后生效。如需调整规格或数量，价格需重新核算。</t>
-  </si>
-  <si>
-    <t>供方签字（盖章）：张报价　____________________</t>
-  </si>
-  <si>
-    <t>需方签字（盖章）：____________________</t>
-  </si>
-  <si>
-    <t>计算明细 · BJ-20260910-6891</t>
-  </si>
-  <si>
-    <t>顺德电器有限公司　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　模芯宽：400 mm　·　模芯长：500 mm　·　模芯高：150 mm　·　单件重量：0.18 kg　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　首单数量：300000 件</t>
-  </si>
-  <si>
-    <t>计算方式与代入过程</t>
+    <t>（二）注塑费用</t>
   </si>
   <si>
     <t>注塑费用合计</t>
   </si>
   <si>
+    <t>注塑单件成本</t>
+  </si>
+  <si>
     <t>利润</t>
   </si>
   <si>
@@ -233,14 +278,18 @@
     <t>含税总价</t>
   </si>
   <si>
-    <t>说明：计算方式由配置中心设定，金额为系统按公式自动核算结果。</t>
+    <t>说明：计算方式由配置中心设定，金额为系统自动核算结果。注塑费用按「单件成本 × 注塑数量」计。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot; 件&quot;"/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -284,7 +333,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <name val="微软雅黑"/>
     </font>
     <font>
@@ -306,6 +355,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF166534"/>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
       <name val="微软雅黑"/>
@@ -314,11 +369,6 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="15"/>
-      <name val="微软雅黑"/>
-    </font>
-    <font>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
       <name val="微软雅黑"/>
     </font>
     <font>
@@ -335,6 +385,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF166534"/>
+      <sz val="10.5"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF1E40AF"/>
       <sz val="12.5"/>
       <name val="微软雅黑"/>
@@ -346,7 +402,7 @@
       <name val="微软雅黑"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -376,6 +432,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0FDF4"/>
       </patternFill>
     </fill>
     <fill>
@@ -411,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -438,15 +499,14 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -459,6 +519,9 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -471,24 +534,41 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="12" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -508,19 +588,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -865,17 +949,18 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -883,8 +968,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -892,8 +978,9 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="2"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -901,18 +988,21 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="5"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="5"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
@@ -920,8 +1010,9 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -935,8 +1026,9 @@
       <c r="E8" s="8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
@@ -950,8 +1042,9 @@
       <c r="E9" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>14</v>
       </c>
@@ -965,8 +1058,9 @@
       <c r="E10" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>17</v>
       </c>
@@ -980,8 +1074,9 @@
       <c r="E11" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -995,8 +1090,9 @@
       <c r="E12" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>20</v>
       </c>
@@ -1010,8 +1106,9 @@
       <c r="E13" s="8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>20</v>
       </c>
@@ -1025,8 +1122,9 @@
       <c r="E14" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>20</v>
       </c>
@@ -1040,8 +1138,9 @@
       <c r="E15" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
@@ -1055,8 +1154,9 @@
       <c r="E16" s="8" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>20</v>
       </c>
@@ -1070,485 +1170,807 @@
       <c r="E17" s="8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="E18" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="E19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="F19" s="8"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="B22" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="13">
+      <c r="C22" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="12">
         <v>67605.5</v>
       </c>
-      <c r="E21" s="12"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="14">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="13">
         <v>1</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="17">
+      <c r="B24" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="17">
         <v>5887.5</v>
       </c>
-      <c r="E22" s="15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="18">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
         <v>2</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="21">
+      <c r="B25" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="22">
         <v>38400</v>
       </c>
-      <c r="E23" s="19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="14">
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="13">
         <v>3</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="17">
+      <c r="B26" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="17">
         <v>6000</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="18">
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
         <v>4</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="21">
+      <c r="B27" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="22">
         <v>5000</v>
       </c>
-      <c r="E25" s="19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="14">
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="13">
         <v>5</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="17">
+      <c r="B28" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="17">
         <v>8818</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="18">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="18">
         <v>6</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="21">
+      <c r="B29" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="22">
         <v>3500</v>
       </c>
-      <c r="E27" s="19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" ht="22" customHeight="1" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C30" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="23">
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="24">
+        <v>13090</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="13">
+        <v>1</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="25">
+        <v>2.27</v>
+      </c>
+      <c r="E31" s="26">
+        <v>5000</v>
+      </c>
+      <c r="F31" s="17">
+        <v>11340</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="18">
+        <v>2</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="E32" s="28">
+        <v>5000</v>
+      </c>
+      <c r="F32" s="22">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="13">
+        <v>3</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="E33" s="26">
+        <v>5000</v>
+      </c>
+      <c r="F33" s="17">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D36" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" s="29"/>
+      <c r="F36" s="30">
         <v>67605.5</v>
       </c>
-      <c r="E30" s="24"/>
-    </row>
-    <row r="31" ht="22" customHeight="1" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C31" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="23">
-        <v>6761</v>
-      </c>
-      <c r="E31" s="24"/>
-    </row>
-    <row r="32" ht="22" customHeight="1" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C32" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="23">
-        <v>9668</v>
-      </c>
-      <c r="E32" s="24"/>
-    </row>
-    <row r="33" ht="36" customHeight="1" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C33" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" s="26">
-        <v>84034.5</v>
-      </c>
-      <c r="E33" s="27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D37" s="29" t="s">
+        <v>66</v>
+      </c>
       <c r="E37" s="29"/>
-    </row>
-    <row r="38" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
+      <c r="F37" s="30">
+        <v>13090</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D38" s="29" t="s">
+        <v>67</v>
+      </c>
       <c r="E38" s="29"/>
-    </row>
-    <row r="39" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
+      <c r="F38" s="30">
+        <v>8070</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D39" s="29" t="s">
+        <v>68</v>
+      </c>
       <c r="E39" s="29"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-    </row>
-    <row r="43" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="B43" s="31"/>
-      <c r="D43" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="E43" s="31"/>
+      <c r="F39" s="30">
+        <v>11540</v>
+      </c>
+    </row>
+    <row r="40" ht="38" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D40" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="31"/>
+      <c r="F40" s="32">
+        <v>100305.5</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+    </row>
+    <row r="45" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+    </row>
+    <row r="46" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" s="35"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="35"/>
+    </row>
+    <row r="50" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A7:E7"/>
+  <mergeCells count="47">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A7:F7"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:F10"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="E12:F12"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="E16:F16"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="D50:F50"/>
   </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-6891</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-3874</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+        <v>41</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="13">
         <v>1</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="17">
+      <c r="B6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="17">
         <v>5887.5</v>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+    <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="18">
         <v>2</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="21">
+      <c r="B7" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="22">
         <v>38400</v>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+    <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13">
         <v>3</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="17">
+      <c r="B8" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="17">
         <v>6000</v>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="18">
+    <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="18">
         <v>4</v>
       </c>
-      <c r="B8" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="21">
+      <c r="B9" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="22">
         <v>5000</v>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+    <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13">
         <v>5</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="17">
+      <c r="B10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="17">
         <v>8818</v>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="18">
+    <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="18">
         <v>6</v>
       </c>
-      <c r="B10" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="21">
+      <c r="B11" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="22">
         <v>3500</v>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="23">
+    <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="13">
+        <v>1</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="25">
+        <v>2.27</v>
+      </c>
+      <c r="E13" s="26">
+        <v>5000</v>
+      </c>
+      <c r="F13" s="17">
+        <v>11340</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="18">
+        <v>2</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="E14" s="28">
+        <v>5000</v>
+      </c>
+      <c r="F14" s="22">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="13">
+        <v>3</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="E15" s="26">
+        <v>5000</v>
+      </c>
+      <c r="F15" s="17">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="41"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="29"/>
+      <c r="F17" s="30">
         <v>67605.5</v>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="23">
-        <v>6761</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="23">
-        <v>9668</v>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="37">
-        <v>84034.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
+    <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="41"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="29"/>
+      <c r="F18" s="30">
+        <v>13090</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="41"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="29"/>
+      <c r="F19" s="42">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="29"/>
+      <c r="F20" s="30">
+        <v>8070</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="41"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="29"/>
+      <c r="F21" s="30">
+        <v>11540</v>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="43"/>
+      <c r="F22" s="44">
+        <v>100305.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A18:D18"/>
+  <mergeCells count="11">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A24:F24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/prototype/sample-quote.xlsx
+++ b/prototype/sample-quote.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="101">
   <si>
     <t>星辉模具制造有限公司</t>
   </si>
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-3874</t>
+    <t>报价编号：BJ-20260910-1135</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -125,6 +125,42 @@
     <t>300000 件</t>
   </si>
   <si>
+    <t>模具重量</t>
+  </si>
+  <si>
+    <t>800 kg</t>
+  </si>
+  <si>
+    <t>运输箱长</t>
+  </si>
+  <si>
+    <t>120 cm</t>
+  </si>
+  <si>
+    <t>运输箱宽</t>
+  </si>
+  <si>
+    <t>100 cm</t>
+  </si>
+  <si>
+    <t>运输箱高</t>
+  </si>
+  <si>
+    <t>80 cm</t>
+  </si>
+  <si>
+    <t>运费单价</t>
+  </si>
+  <si>
+    <t>1.2 元/kg</t>
+  </si>
+  <si>
+    <t>运输区域</t>
+  </si>
+  <si>
+    <t>广东省外</t>
+  </si>
+  <si>
     <t>二、费用明细</t>
   </si>
   <si>
@@ -173,10 +209,10 @@
     <t>腔数 × 2500 元</t>
   </si>
   <si>
-    <t>管理费</t>
-  </si>
-  <si>
-    <t>模具小计 × 15%</t>
+    <t>运输费</t>
+  </si>
+  <si>
+    <t>最大值 ( 模具重量, 运输箱长 × 运输箱宽 × 运输箱高 ÷ 6000 ) × 运费单价 × 运输区域</t>
   </si>
   <si>
     <t>差旅费</t>
@@ -224,7 +260,7 @@
     <t>含 税 总 价</t>
   </si>
   <si>
-    <t>大写金额：壹拾万零叁佰零伍元伍角</t>
+    <t>大写金额：玖万零伍佰叁拾柒元伍角</t>
   </si>
   <si>
     <t>四、商务条款</t>
@@ -233,7 +269,7 @@
     <t>1. 以上总价含 13% 增值税，开具增值税专用发票。</t>
   </si>
   <si>
-    <t>2. 广东省内运费免费，省外按实际运输方式另行计费。</t>
+    <t>2. 运费：广东省内免运费；省外运费已按模具重量与包装体积核算，并包含在上述总价内。</t>
   </si>
   <si>
     <t>3. 模具 40 天交货，首单注塑于收到定金后 45 天交付。</t>
@@ -248,10 +284,10 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-3874</t>
-  </si>
-  <si>
-    <t>顺德电器有限公司　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件</t>
+    <t>计算明细 · BJ-20260910-1135</t>
+  </si>
+  <si>
+    <t>顺德电器有限公司　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省外</t>
   </si>
   <si>
     <t>计算方式与代入过程</t>
@@ -949,7 +985,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1204,369 +1240,465 @@
       </c>
       <c r="F19" s="8"/>
     </row>
-    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+    <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="E20" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="F20" s="8"/>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="E23" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="12">
-        <v>67605.5</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="13">
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="12">
+        <v>59747.5</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="13">
         <v>1</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="17">
+      <c r="B30" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="17">
         <v>5887.5</v>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="18">
+    <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="18">
         <v>2</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="22">
+      <c r="B31" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="22">
         <v>38400</v>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="13">
+    <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="13">
         <v>3</v>
       </c>
-      <c r="B26" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="17">
+      <c r="B32" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="17">
         <v>6000</v>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="18">
+    <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="18">
         <v>4</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="22">
+      <c r="B33" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="22">
         <v>5000</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="13">
+    <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="13">
         <v>5</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="17">
-        <v>8818</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="18">
+      <c r="B34" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="17">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="18">
         <v>6</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="22">
+      <c r="B35" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="22">
         <v>3500</v>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="24">
+    <row r="36" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="24">
         <v>13090</v>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="13">
+    <row r="37" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="13">
         <v>1</v>
       </c>
-      <c r="B31" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="25">
+      <c r="B37" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="25">
         <v>2.27</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E37" s="26">
         <v>5000</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F37" s="17">
         <v>11340</v>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="18">
+    <row r="38" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="18">
         <v>2</v>
       </c>
-      <c r="B32" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D32" s="27">
+      <c r="B38" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="27">
         <v>0.3</v>
       </c>
-      <c r="E32" s="28">
+      <c r="E38" s="28">
         <v>5000</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F38" s="22">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="13">
+    <row r="39" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="13">
         <v>3</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D33" s="25">
+      <c r="B39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="25">
         <v>0.05</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E39" s="26">
         <v>5000</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F39" s="17">
         <v>250</v>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D36" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="E36" s="29"/>
-      <c r="F36" s="30">
-        <v>67605.5</v>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D37" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="E37" s="29"/>
-      <c r="F37" s="30">
+    <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D42" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E42" s="29"/>
+      <c r="F42" s="30">
+        <v>59747.5</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D43" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" s="29"/>
+      <c r="F43" s="30">
         <v>13090</v>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D38" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="E38" s="29"/>
-      <c r="F38" s="30">
-        <v>8070</v>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D39" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="E39" s="29"/>
-      <c r="F39" s="30">
-        <v>11540</v>
-      </c>
-    </row>
-    <row r="40" ht="38" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D40" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="E40" s="31"/>
-      <c r="F40" s="32">
-        <v>100305.5</v>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="B41" s="33"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-    </row>
-    <row r="43" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-    </row>
-    <row r="44" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-    </row>
-    <row r="45" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-    </row>
-    <row r="46" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="B46" s="34"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48" s="35"/>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="35"/>
-    </row>
-    <row r="50" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="B50" s="36"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
+    <row r="44" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D44" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="29"/>
+      <c r="F44" s="30">
+        <v>7284</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D45" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="29"/>
+      <c r="F45" s="30">
+        <v>10416</v>
+      </c>
+    </row>
+    <row r="46" ht="38" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D46" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" s="31"/>
+      <c r="F46" s="32">
+        <v>90537.5</v>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
+    </row>
+    <row r="49" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" s="34"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="B54" s="35"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="35"/>
+    </row>
+    <row r="56" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B56" s="36"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="59">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
@@ -1597,28 +1729,40 @@
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="D56:F56"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-3874</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-1135</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1638,7 +1782,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -1648,7 +1792,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -1658,27 +1802,27 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B5" s="39"/>
       <c r="C5" s="39"/>
@@ -1691,10 +1835,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>11</v>
@@ -1711,10 +1855,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>11</v>
@@ -1731,10 +1875,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>11</v>
@@ -1751,10 +1895,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>11</v>
@@ -1771,10 +1915,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>11</v>
@@ -1783,7 +1927,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="17">
-        <v>8818</v>
+        <v>960</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1791,10 +1935,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>11</v>
@@ -1808,7 +1952,7 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="40" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B12" s="40"/>
       <c r="C12" s="40"/>
@@ -1821,10 +1965,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D13" s="25">
         <v>2.27</v>
@@ -1841,10 +1985,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D14" s="27">
         <v>0.3</v>
@@ -1861,10 +2005,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D15" s="25">
         <v>0.05</v>
@@ -1881,11 +2025,11 @@
       <c r="B17" s="41"/>
       <c r="C17" s="41"/>
       <c r="D17" s="29" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E17" s="29"/>
       <c r="F17" s="30">
-        <v>67605.5</v>
+        <v>59747.5</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1893,7 +2037,7 @@
       <c r="B18" s="41"/>
       <c r="C18" s="41"/>
       <c r="D18" s="29" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E18" s="29"/>
       <c r="F18" s="30">
@@ -1905,7 +2049,7 @@
       <c r="B19" s="41"/>
       <c r="C19" s="41"/>
       <c r="D19" s="29" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E19" s="29"/>
       <c r="F19" s="42">
@@ -1917,11 +2061,11 @@
       <c r="B20" s="41"/>
       <c r="C20" s="41"/>
       <c r="D20" s="29" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E20" s="29"/>
       <c r="F20" s="30">
-        <v>8070</v>
+        <v>7284</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1929,11 +2073,11 @@
       <c r="B21" s="41"/>
       <c r="C21" s="41"/>
       <c r="D21" s="29" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E21" s="29"/>
       <c r="F21" s="30">
-        <v>11540</v>
+        <v>10416</v>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1941,16 +2085,16 @@
       <c r="B22" s="41"/>
       <c r="C22" s="41"/>
       <c r="D22" s="43" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E22" s="43"/>
       <c r="F22" s="44">
-        <v>100305.5</v>
+        <v>90537.5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="45" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B24" s="45"/>
       <c r="C24" s="45"/>

--- a/prototype/sample-quote.xlsx
+++ b/prototype/sample-quote.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-1135</t>
+    <t>报价编号：BJ-20260910-6348</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -284,7 +284,7 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-1135</t>
+    <t>计算明细 · BJ-20260910-6348</t>
   </si>
   <si>
     <t>顺德电器有限公司　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省外</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-1135</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-6348</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/prototype/sample-quote.xlsx
+++ b/prototype/sample-quote.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-6348</t>
+    <t>报价编号：BJ-20260910-6882</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -284,7 +284,7 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-6348</t>
+    <t>计算明细 · BJ-20260910-6882</t>
   </si>
   <si>
     <t>顺德电器有限公司　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省外</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-6348</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-6882</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/prototype/sample-quote.xlsx
+++ b/prototype/sample-quote.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-6882</t>
+    <t>报价编号：BJ-20260910-3799</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -284,7 +284,7 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-6882</t>
+    <t>计算明细 · BJ-20260910-3799</t>
   </si>
   <si>
     <t>顺德电器有限公司　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省外</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-6882</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-3799</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/prototype/sample-quote.xlsx
+++ b/prototype/sample-quote.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-3799</t>
+    <t>报价编号：BJ-20260910-9442</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -284,7 +284,7 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-3799</t>
+    <t>计算明细 · BJ-20260910-9442</t>
   </si>
   <si>
     <t>顺德电器有限公司　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省外</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-3799</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-9442</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/prototype/sample-quote.xlsx
+++ b/prototype/sample-quote.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-9442</t>
+    <t>报价编号：BJ-20260910-9995</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -284,7 +284,7 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-9442</t>
+    <t>计算明细 · BJ-20260910-9995</t>
   </si>
   <si>
     <t>顺德电器有限公司　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省外</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-9442</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-9995</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/prototype/sample-quote.xlsx
+++ b/prototype/sample-quote.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-9995</t>
+    <t>报价编号：BJ-20260910-3680</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -119,46 +119,46 @@
     <t>5000 件</t>
   </si>
   <si>
+    <t>模具重量</t>
+  </si>
+  <si>
+    <t>800 kg</t>
+  </si>
+  <si>
+    <t>运输箱长</t>
+  </si>
+  <si>
+    <t>120 cm</t>
+  </si>
+  <si>
+    <t>运输箱宽</t>
+  </si>
+  <si>
+    <t>100 cm</t>
+  </si>
+  <si>
+    <t>运输箱高</t>
+  </si>
+  <si>
+    <t>80 cm</t>
+  </si>
+  <si>
+    <t>运费单价</t>
+  </si>
+  <si>
+    <t>1.2 元/kg</t>
+  </si>
+  <si>
+    <t>运输区域</t>
+  </si>
+  <si>
+    <t>广东省外</t>
+  </si>
+  <si>
     <t>首单数量</t>
   </si>
   <si>
-    <t>300000 件</t>
-  </si>
-  <si>
-    <t>模具重量</t>
-  </si>
-  <si>
-    <t>800 kg</t>
-  </si>
-  <si>
-    <t>运输箱长</t>
-  </si>
-  <si>
-    <t>120 cm</t>
-  </si>
-  <si>
-    <t>运输箱宽</t>
-  </si>
-  <si>
-    <t>100 cm</t>
-  </si>
-  <si>
-    <t>运输箱高</t>
-  </si>
-  <si>
-    <t>80 cm</t>
-  </si>
-  <si>
-    <t>运费单价</t>
-  </si>
-  <si>
-    <t>1.2 元/kg</t>
-  </si>
-  <si>
-    <t>运输区域</t>
-  </si>
-  <si>
-    <t>广东省外</t>
+    <t>300000</t>
   </si>
   <si>
     <t>二、费用明细</t>
@@ -284,10 +284,10 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-9995</t>
-  </si>
-  <si>
-    <t>顺德电器有限公司　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省外</t>
+    <t>计算明细 · BJ-20260910-3680</t>
+  </si>
+  <si>
+    <t>顺德电器有限公司　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省外　·　首单数量：300000</t>
   </si>
   <si>
     <t>计算方式与代入过程</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-9995</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-3680</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
